--- a/labs/lab-06-filters-and-refresh/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-06-filters-and-refresh/data/Northstar_Work_Orders.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Northstar Facilities - fictional</t>
+          <t>Northstar Water Services - fictional water-pipe maintenance and service company</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 001</t>
+          <t>Leak Repair scheduled or reactive task 001</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 002</t>
+          <t>Leak Repair scheduled or reactive task 002</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 003</t>
+          <t>Leak Repair scheduled or reactive task 003</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 004</t>
+          <t>Leak Repair scheduled or reactive task 004</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 005</t>
+          <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 006</t>
+          <t>Valve Repair scheduled or reactive task 006</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 007</t>
+          <t>Valve Repair scheduled or reactive task 007</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 008</t>
+          <t>Valve Repair scheduled or reactive task 008</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 009</t>
+          <t>Pipe Replacement scheduled or reactive task 009</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 010</t>
+          <t>Pipe Replacement scheduled or reactive task 010</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 011</t>
+          <t>Pipe Replacement scheduled or reactive task 011</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 012</t>
+          <t>Pipe Replacement scheduled or reactive task 012</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 013</t>
+          <t>Pump Service scheduled or reactive task 013</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 014</t>
+          <t>Pump Service scheduled or reactive task 014</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 015</t>
+          <t>Pump Service scheduled or reactive task 015</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 016</t>
+          <t>Pump Service scheduled or reactive task 016</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 017</t>
+          <t>Meter Service scheduled or reactive task 017</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 018</t>
+          <t>Meter Service scheduled or reactive task 018</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 019</t>
+          <t>Meter Service scheduled or reactive task 019</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 020</t>
+          <t>Meter Service scheduled or reactive task 020</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 021</t>
+          <t>Leak Repair scheduled or reactive task 021</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 022</t>
+          <t>Leak Repair scheduled or reactive task 022</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 023</t>
+          <t>Leak Repair scheduled or reactive task 023</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 024</t>
+          <t>Leak Repair scheduled or reactive task 024</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 025</t>
+          <t>Valve Repair scheduled or reactive task 025</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 026</t>
+          <t>Valve Repair scheduled or reactive task 026</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 027</t>
+          <t>Valve Repair scheduled or reactive task 027</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 028</t>
+          <t>Valve Repair scheduled or reactive task 028</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 029</t>
+          <t>Pipe Replacement scheduled or reactive task 029</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 030</t>
+          <t>Pipe Replacement scheduled or reactive task 030</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 031</t>
+          <t>Pipe Replacement scheduled or reactive task 031</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 032</t>
+          <t>Pipe Replacement scheduled or reactive task 032</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 033</t>
+          <t>Pump Service scheduled or reactive task 033</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 034</t>
+          <t>Pump Service scheduled or reactive task 034</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 035</t>
+          <t>Pump Service scheduled or reactive task 035</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 036</t>
+          <t>Pump Service scheduled or reactive task 036</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 037</t>
+          <t>Meter Service scheduled or reactive task 037</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 038</t>
+          <t>Meter Service scheduled or reactive task 038</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 039</t>
+          <t>Meter Service scheduled or reactive task 039</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 040</t>
+          <t>Meter Service scheduled or reactive task 040</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 041</t>
+          <t>Leak Repair scheduled or reactive task 041</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 042</t>
+          <t>Leak Repair scheduled or reactive task 042</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 043</t>
+          <t>Leak Repair scheduled or reactive task 043</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 044</t>
+          <t>Leak Repair scheduled or reactive task 044</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 045</t>
+          <t>Valve Repair scheduled or reactive task 045</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 046</t>
+          <t>Valve Repair scheduled or reactive task 046</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 047</t>
+          <t>Valve Repair scheduled or reactive task 047</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 048</t>
+          <t>Valve Repair scheduled or reactive task 048</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 049</t>
+          <t>Pipe Replacement scheduled or reactive task 049</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 050</t>
+          <t>Pipe Replacement scheduled or reactive task 050</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 051</t>
+          <t>Pipe Replacement scheduled or reactive task 051</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 052</t>
+          <t>Pipe Replacement scheduled or reactive task 052</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 053</t>
+          <t>Pump Service scheduled or reactive task 053</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 054</t>
+          <t>Pump Service scheduled or reactive task 054</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 055</t>
+          <t>Pump Service scheduled or reactive task 055</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 056</t>
+          <t>Pump Service scheduled or reactive task 056</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 057</t>
+          <t>Meter Service scheduled or reactive task 057</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 058</t>
+          <t>Meter Service scheduled or reactive task 058</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 059</t>
+          <t>Meter Service scheduled or reactive task 059</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 060</t>
+          <t>Meter Service scheduled or reactive task 060</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 061</t>
+          <t>Leak Repair scheduled or reactive task 061</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 062</t>
+          <t>Leak Repair scheduled or reactive task 062</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 063</t>
+          <t>Leak Repair scheduled or reactive task 063</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 064</t>
+          <t>Leak Repair scheduled or reactive task 064</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 065</t>
+          <t>Valve Repair scheduled or reactive task 065</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 066</t>
+          <t>Valve Repair scheduled or reactive task 066</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 067</t>
+          <t>Valve Repair scheduled or reactive task 067</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 068</t>
+          <t>Valve Repair scheduled or reactive task 068</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 069</t>
+          <t>Pipe Replacement scheduled or reactive task 069</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 070</t>
+          <t>Pipe Replacement scheduled or reactive task 070</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 071</t>
+          <t>Pipe Replacement scheduled or reactive task 071</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 072</t>
+          <t>Pipe Replacement scheduled or reactive task 072</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 073</t>
+          <t>Pump Service scheduled or reactive task 073</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 074</t>
+          <t>Pump Service scheduled or reactive task 074</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 075</t>
+          <t>Pump Service scheduled or reactive task 075</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 076</t>
+          <t>Pump Service scheduled or reactive task 076</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 077</t>
+          <t>Meter Service scheduled or reactive task 077</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 078</t>
+          <t>Meter Service scheduled or reactive task 078</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 079</t>
+          <t>Meter Service scheduled or reactive task 079</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 080</t>
+          <t>Meter Service scheduled or reactive task 080</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 081</t>
+          <t>Leak Repair scheduled or reactive task 081</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 082</t>
+          <t>Leak Repair scheduled or reactive task 082</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 083</t>
+          <t>Leak Repair scheduled or reactive task 083</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 084</t>
+          <t>Leak Repair scheduled or reactive task 084</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 085</t>
+          <t>Valve Repair scheduled or reactive task 085</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 086</t>
+          <t>Valve Repair scheduled or reactive task 086</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 087</t>
+          <t>Valve Repair scheduled or reactive task 087</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 088</t>
+          <t>Valve Repair scheduled or reactive task 088</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 089</t>
+          <t>Pipe Replacement scheduled or reactive task 089</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 090</t>
+          <t>Pipe Replacement scheduled or reactive task 090</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 091</t>
+          <t>Pipe Replacement scheduled or reactive task 091</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 092</t>
+          <t>Pipe Replacement scheduled or reactive task 092</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 093</t>
+          <t>Pump Service scheduled or reactive task 093</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 094</t>
+          <t>Pump Service scheduled or reactive task 094</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 095</t>
+          <t>Pump Service scheduled or reactive task 095</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 096</t>
+          <t>Pump Service scheduled or reactive task 096</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 097</t>
+          <t>Meter Service scheduled or reactive task 097</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 098</t>
+          <t>Meter Service scheduled or reactive task 098</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 099</t>
+          <t>Meter Service scheduled or reactive task 099</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 100</t>
+          <t>Meter Service scheduled or reactive task 100</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 101</t>
+          <t>Leak Repair scheduled or reactive task 101</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 102</t>
+          <t>Leak Repair scheduled or reactive task 102</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 103</t>
+          <t>Leak Repair scheduled or reactive task 103</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 104</t>
+          <t>Leak Repair scheduled or reactive task 104</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 105</t>
+          <t>Valve Repair scheduled or reactive task 105</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 106</t>
+          <t>Valve Repair scheduled or reactive task 106</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 107</t>
+          <t>Valve Repair scheduled or reactive task 107</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 108</t>
+          <t>Valve Repair scheduled or reactive task 108</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 109</t>
+          <t>Pipe Replacement scheduled or reactive task 109</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 110</t>
+          <t>Pipe Replacement scheduled or reactive task 110</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 111</t>
+          <t>Pipe Replacement scheduled or reactive task 111</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 112</t>
+          <t>Pipe Replacement scheduled or reactive task 112</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 113</t>
+          <t>Pump Service scheduled or reactive task 113</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 114</t>
+          <t>Pump Service scheduled or reactive task 114</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 115</t>
+          <t>Pump Service scheduled or reactive task 115</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 116</t>
+          <t>Pump Service scheduled or reactive task 116</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 117</t>
+          <t>Meter Service scheduled or reactive task 117</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 118</t>
+          <t>Meter Service scheduled or reactive task 118</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 119</t>
+          <t>Meter Service scheduled or reactive task 119</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 120</t>
+          <t>Meter Service scheduled or reactive task 120</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -7823,7 +7823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7869,15 +7869,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY:
+Before testing filters, report the baseline Northstar Water Services dashboard source, date and scope. Confirm 120 unique work orders and all four selectors All. Identify the baseline file that must remain untouched when making the refresh-test copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>EXCEL - PLAN</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>EXCEL - PLAN:
 Make Dashboard B2:B5 control all six KPIs and three chart summaries with AND logic. All bypasses its dimension. Use COUNTIFS/SUMIFS or SUMPRODUCT with structured table references. Blank owner means unassigned and must not disappear from All. Keep N/A for no closed jobs.
@@ -7886,39 +7904,75 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Step 3</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>EXCEL - CHAT ONLY</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>EXCEL - CHAT ONLY:
 For the dashboard selection Site = Woodlands Hub and all other dimensions All, list the expected six KPI values from tblWorkOrders and verify each chart sum matches the selected total. Do not infer that filtering the worksheet automatically changes formula measures.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY:
+Check two dashboard edge cases without changing source data: Status New with other selectors All; then Site Woodlands Hub, Job_Category Leak Repair, Assigned_To Daniel Lee, Status All. Verify zero closed gives N/A and no selected rows gives zero count/cost with N/A rate. Show how all charts follow the same selection. Restore all selectors to All.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Step 6</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>EXCEL - CHAT ONLY</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>EXCEL - CHAT ONLY:
 Verify the sandbox append test for the two new work orders. Reconcile total 122, closed 49, backlog 61, overdue increased by 1, cost increased by S$400 and on-time numerator increased by 1. Confirm no original source record changed and all three charts total 122 with All selections. Compare original IDs, statuses, owners, dates and costs to the saved baseline; all original 120 rows must match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Step 7</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>WORD COPILOT</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>WORD COPILOT:
+Using only the verified baseline dashboard evidence I paste here, prepare the frozen Northstar Water Services presentation snapshot. Include reporting date, All scope, 120-row baseline, six KPIs, chart values, source workbook link and limitations. Exclude the 122-row sandbox. Keep proposed priorities separate from observed facts.</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8349,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -8308,7 +8362,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="B26" s="2">
@@ -8321,7 +8375,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="B27" s="2">
@@ -8334,7 +8388,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="B28" s="2">
@@ -8347,7 +8401,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="B29" s="2">
@@ -8514,7 +8568,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8536,7 +8590,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8558,7 +8612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8580,7 +8634,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8602,7 +8656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
